--- a/compounds_trivial.xlsx
+++ b/compounds_trivial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{7FF3A1EB-A75C-45BC-8D03-EFC863ADCF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC834875-A204-4C2A-8BB6-2A7CD14D9B7C}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{7FF3A1EB-A75C-45BC-8D03-EFC863ADCF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7F862D-AF94-48A8-B5E2-AFA59A2A3AB3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FAABE964-FAF7-4589-B996-F178970E1676}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="381">
   <si>
     <t>structure</t>
   </si>
@@ -593,9 +593,6 @@
     <t>6-Aminopurine</t>
   </si>
   <si>
-    <t>Nc1nc2c(n[nH]c2=O)[nH]1</t>
-  </si>
-  <si>
     <t>Guanine</t>
   </si>
   <si>
@@ -1002,6 +999,189 @@
   </si>
   <si>
     <t>シアン酸 (分子として)</t>
+  </si>
+  <si>
+    <t>O=c1[nH]c(N)nc2[nH]cnc12</t>
+  </si>
+  <si>
+    <t>NCC(=O)O</t>
+  </si>
+  <si>
+    <t>Gly</t>
+  </si>
+  <si>
+    <t>Glycine</t>
+  </si>
+  <si>
+    <t>C[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Ala</t>
+  </si>
+  <si>
+    <t>Alanine</t>
+  </si>
+  <si>
+    <t>CC(C)[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Val</t>
+  </si>
+  <si>
+    <t>Valine</t>
+  </si>
+  <si>
+    <t>CC(C)C[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Leu</t>
+  </si>
+  <si>
+    <t>Leucine</t>
+  </si>
+  <si>
+    <t>CC[C@H](C)[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Ile</t>
+  </si>
+  <si>
+    <t>Isoleucine</t>
+  </si>
+  <si>
+    <t>O=C(O)[C@@H]1CCCN1</t>
+  </si>
+  <si>
+    <t>Pro</t>
+  </si>
+  <si>
+    <t>Proline</t>
+  </si>
+  <si>
+    <t>N[C@@H](Cc1ccccc1)C(=O)O</t>
+  </si>
+  <si>
+    <t>Phe</t>
+  </si>
+  <si>
+    <t>Phenylalanine</t>
+  </si>
+  <si>
+    <t>N[C@@H](Cc1ccc(O)cc1)C(=O)O</t>
+  </si>
+  <si>
+    <t>Tyr</t>
+  </si>
+  <si>
+    <t>Tyrosine</t>
+  </si>
+  <si>
+    <t>N[C@@H](Cc1c[nH]c2ccccc12)C(=O)O</t>
+  </si>
+  <si>
+    <t>Trp</t>
+  </si>
+  <si>
+    <t>Tryptophan</t>
+  </si>
+  <si>
+    <t>OC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Ser</t>
+  </si>
+  <si>
+    <t>Serine</t>
+  </si>
+  <si>
+    <t>C[C@H](O)[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Thr</t>
+  </si>
+  <si>
+    <t>Threonine</t>
+  </si>
+  <si>
+    <t>SC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Cys</t>
+  </si>
+  <si>
+    <t>Cysteine</t>
+  </si>
+  <si>
+    <t>CSCC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
+    <t>Methionine</t>
+  </si>
+  <si>
+    <t>NC(=O)C[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Asn</t>
+  </si>
+  <si>
+    <t>Asparagine</t>
+  </si>
+  <si>
+    <t>NC(=O)CC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Gln</t>
+  </si>
+  <si>
+    <t>Glutamine</t>
+  </si>
+  <si>
+    <t>O=C(O)C[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Asp</t>
+  </si>
+  <si>
+    <t>Aspartic acid</t>
+  </si>
+  <si>
+    <t>O=C(O)CC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Glu</t>
+  </si>
+  <si>
+    <t>Glutamic acid</t>
+  </si>
+  <si>
+    <t>NCCCC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Lys</t>
+  </si>
+  <si>
+    <t>Lysine</t>
+  </si>
+  <si>
+    <t>NC(=N)NCCC[C@@H](N)C(=O)O</t>
+  </si>
+  <si>
+    <t>Arg</t>
+  </si>
+  <si>
+    <t>Arginine</t>
+  </si>
+  <si>
+    <t>N[C@@H](Cc1c[nH]cn1)C(=O)O</t>
+  </si>
+  <si>
+    <t>His</t>
+  </si>
+  <si>
+    <t>Histidine</t>
   </si>
 </sst>
 </file>
@@ -1076,6 +1256,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1395,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4322499-08B3-4EA7-81EC-51E90C578178}">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2093,508 +2277,728 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" t="s">
         <v>184</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>185</v>
-      </c>
-      <c r="C64" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" t="s">
         <v>187</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>188</v>
-      </c>
-      <c r="C65" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" t="s">
         <v>190</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>191</v>
-      </c>
-      <c r="C66" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
+        <v>192</v>
+      </c>
+      <c r="B67" t="s">
         <v>193</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>194</v>
-      </c>
-      <c r="C67" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" t="s">
         <v>196</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>197</v>
-      </c>
-      <c r="C68" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
+        <v>198</v>
+      </c>
+      <c r="B69" t="s">
         <v>199</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>200</v>
-      </c>
-      <c r="C69" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
+        <v>201</v>
+      </c>
+      <c r="B70" t="s">
         <v>202</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>203</v>
-      </c>
-      <c r="C70" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
+        <v>204</v>
+      </c>
+      <c r="B71" t="s">
         <v>205</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>206</v>
-      </c>
-      <c r="C71" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
+        <v>207</v>
+      </c>
+      <c r="B72" t="s">
         <v>208</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>209</v>
-      </c>
-      <c r="C72" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
+        <v>210</v>
+      </c>
+      <c r="B73" t="s">
         <v>211</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>212</v>
-      </c>
-      <c r="C73" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" t="s">
         <v>214</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>215</v>
-      </c>
-      <c r="C74" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
+        <v>216</v>
+      </c>
+      <c r="B75" t="s">
         <v>217</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>218</v>
-      </c>
-      <c r="C75" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
+        <v>219</v>
+      </c>
+      <c r="B76" t="s">
         <v>220</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>221</v>
-      </c>
-      <c r="C76" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
+        <v>222</v>
+      </c>
+      <c r="B77" t="s">
         <v>223</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>224</v>
-      </c>
-      <c r="C77" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" t="s">
         <v>226</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>227</v>
-      </c>
-      <c r="C78" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
+        <v>228</v>
+      </c>
+      <c r="B79" t="s">
         <v>229</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>230</v>
-      </c>
-      <c r="C79" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
+        <v>231</v>
+      </c>
+      <c r="B80" t="s">
         <v>232</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>233</v>
-      </c>
-      <c r="C80" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
+        <v>234</v>
+      </c>
+      <c r="B81" t="s">
         <v>235</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>236</v>
-      </c>
-      <c r="C81" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
+        <v>237</v>
+      </c>
+      <c r="B82" t="s">
         <v>238</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>239</v>
-      </c>
-      <c r="C82" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
+        <v>240</v>
+      </c>
+      <c r="B83" t="s">
         <v>241</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>242</v>
-      </c>
-      <c r="C83" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
+        <v>243</v>
+      </c>
+      <c r="B84" t="s">
         <v>244</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>245</v>
-      </c>
-      <c r="C84" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
+        <v>246</v>
+      </c>
+      <c r="B85" t="s">
         <v>247</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>248</v>
-      </c>
-      <c r="C85" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
+        <v>249</v>
+      </c>
+      <c r="B86" t="s">
         <v>250</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>251</v>
-      </c>
-      <c r="C86" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
+        <v>252</v>
+      </c>
+      <c r="B87" t="s">
         <v>253</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>254</v>
-      </c>
-      <c r="C87" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
+        <v>255</v>
+      </c>
+      <c r="B88" t="s">
         <v>256</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>257</v>
-      </c>
-      <c r="C88" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
+        <v>258</v>
+      </c>
+      <c r="B89" t="s">
         <v>259</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>260</v>
-      </c>
-      <c r="C89" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
+        <v>261</v>
+      </c>
+      <c r="B90" t="s">
         <v>262</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>263</v>
-      </c>
-      <c r="C90" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
+        <v>264</v>
+      </c>
+      <c r="B91" t="s">
         <v>265</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>266</v>
-      </c>
-      <c r="C91" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
+        <v>267</v>
+      </c>
+      <c r="B92" t="s">
         <v>268</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>269</v>
-      </c>
-      <c r="C92" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
+        <v>270</v>
+      </c>
+      <c r="B93" t="s">
         <v>271</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>272</v>
-      </c>
-      <c r="C93" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
+        <v>273</v>
+      </c>
+      <c r="B94" t="s">
         <v>274</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>275</v>
-      </c>
-      <c r="C94" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
+        <v>276</v>
+      </c>
+      <c r="B95" t="s">
         <v>277</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>278</v>
-      </c>
-      <c r="C95" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
+        <v>279</v>
+      </c>
+      <c r="B96" t="s">
         <v>280</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>281</v>
-      </c>
-      <c r="C96" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
+        <v>282</v>
+      </c>
+      <c r="B97" t="s">
         <v>283</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>284</v>
-      </c>
-      <c r="C97" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
+        <v>285</v>
+      </c>
+      <c r="B98" t="s">
         <v>286</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>287</v>
-      </c>
-      <c r="C98" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
+        <v>288</v>
+      </c>
+      <c r="B99" t="s">
         <v>289</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>290</v>
-      </c>
-      <c r="C99" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
+        <v>291</v>
+      </c>
+      <c r="B100" t="s">
         <v>292</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>293</v>
-      </c>
-      <c r="C100" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
+        <v>294</v>
+      </c>
+      <c r="B101" t="s">
         <v>295</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>296</v>
-      </c>
-      <c r="C101" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
+        <v>297</v>
+      </c>
+      <c r="B102" t="s">
         <v>298</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>299</v>
-      </c>
-      <c r="C102" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
+        <v>300</v>
+      </c>
+      <c r="B103" t="s">
         <v>301</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>302</v>
-      </c>
-      <c r="C103" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
+        <v>303</v>
+      </c>
+      <c r="B104" t="s">
         <v>304</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>305</v>
-      </c>
-      <c r="C104" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
+        <v>306</v>
+      </c>
+      <c r="B105" t="s">
         <v>307</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>308</v>
-      </c>
-      <c r="C105" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
+        <v>309</v>
+      </c>
+      <c r="B106" t="s">
         <v>310</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>311</v>
-      </c>
-      <c r="C106" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
+        <v>312</v>
+      </c>
+      <c r="B107" t="s">
         <v>313</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>314</v>
-      </c>
-      <c r="C107" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B108" t="s">
+        <v>315</v>
+      </c>
+      <c r="C108" t="s">
         <v>316</v>
-      </c>
-      <c r="C108" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="s">
         <v>318</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>319</v>
       </c>
-      <c r="C109" t="s">
-        <v>320</v>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>321</v>
+      </c>
+      <c r="B110" t="s">
+        <v>322</v>
+      </c>
+      <c r="C110" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>324</v>
+      </c>
+      <c r="B111" t="s">
+        <v>325</v>
+      </c>
+      <c r="C111" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>327</v>
+      </c>
+      <c r="B112" t="s">
+        <v>328</v>
+      </c>
+      <c r="C112" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>330</v>
+      </c>
+      <c r="B113" t="s">
+        <v>331</v>
+      </c>
+      <c r="C113" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>333</v>
+      </c>
+      <c r="B114" t="s">
+        <v>334</v>
+      </c>
+      <c r="C114" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>336</v>
+      </c>
+      <c r="B115" t="s">
+        <v>337</v>
+      </c>
+      <c r="C115" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>339</v>
+      </c>
+      <c r="B116" t="s">
+        <v>340</v>
+      </c>
+      <c r="C116" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" t="s">
+        <v>342</v>
+      </c>
+      <c r="B117" t="s">
+        <v>343</v>
+      </c>
+      <c r="C117" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>345</v>
+      </c>
+      <c r="B118" t="s">
+        <v>346</v>
+      </c>
+      <c r="C118" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>348</v>
+      </c>
+      <c r="B119" t="s">
+        <v>349</v>
+      </c>
+      <c r="C119" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" t="s">
+        <v>351</v>
+      </c>
+      <c r="B120" t="s">
+        <v>352</v>
+      </c>
+      <c r="C120" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" t="s">
+        <v>354</v>
+      </c>
+      <c r="B121" t="s">
+        <v>355</v>
+      </c>
+      <c r="C121" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" t="s">
+        <v>357</v>
+      </c>
+      <c r="B122" t="s">
+        <v>358</v>
+      </c>
+      <c r="C122" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" t="s">
+        <v>360</v>
+      </c>
+      <c r="B123" t="s">
+        <v>361</v>
+      </c>
+      <c r="C123" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" t="s">
+        <v>363</v>
+      </c>
+      <c r="B124" t="s">
+        <v>364</v>
+      </c>
+      <c r="C124" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>366</v>
+      </c>
+      <c r="B125" t="s">
+        <v>367</v>
+      </c>
+      <c r="C125" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" t="s">
+        <v>369</v>
+      </c>
+      <c r="B126" t="s">
+        <v>370</v>
+      </c>
+      <c r="C126" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" t="s">
+        <v>372</v>
+      </c>
+      <c r="B127" t="s">
+        <v>373</v>
+      </c>
+      <c r="C127" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" t="s">
+        <v>375</v>
+      </c>
+      <c r="B128" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
+        <v>378</v>
+      </c>
+      <c r="B129" t="s">
+        <v>379</v>
+      </c>
+      <c r="C129" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
